--- a/Side Bar Files/GWD Data/Electrical Essentials.xlsx
+++ b/Side Bar Files/GWD Data/Electrical Essentials.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -361,20 +361,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Sans-serif"/>
+      <name val="Cambria"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Sans-serif"/>
+      <name val="Cambria"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -427,62 +421,42 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -904,7 +878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F15B5F-561B-4BA6-8790-E427F828B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6397824-B5C6-47E4-851F-6BBC5B6BBAA6}">
   <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -1136,13 +1110,13 @@
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C17" s="2">
         <v>33.78</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1156,7 +1130,7 @@
       <c r="C18" s="2">
         <v>52.87</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1170,7 +1144,7 @@
       <c r="C19" s="2">
         <v>71.96</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1184,7 +1158,7 @@
       <c r="C20" s="2">
         <v>91.05</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1198,7 +1172,7 @@
       <c r="C21" s="2">
         <v>117.48</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1212,7 +1186,7 @@
       <c r="C22" s="2">
         <v>136.57</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1226,7 +1200,7 @@
       <c r="C23" s="2">
         <v>163</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1240,7 +1214,7 @@
       <c r="C24" s="2">
         <v>182.09</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1254,7 +1228,7 @@
       <c r="C25" s="2">
         <v>215.87</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1268,7 +1242,7 @@
       <c r="C26" s="2">
         <v>234.96</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1282,7 +1256,7 @@
       <c r="C27" s="2">
         <v>74.08</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1296,7 +1270,7 @@
       <c r="C28" s="2">
         <v>103.77</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1310,7 +1284,7 @@
       <c r="C29" s="2">
         <v>133.47</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1324,7 +1298,7 @@
       <c r="C30" s="2">
         <v>170.51</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1338,7 +1312,7 @@
       <c r="C31" s="2">
         <v>200.20</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1352,7 +1326,7 @@
       <c r="C32" s="2">
         <v>237.24</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1366,7 +1340,7 @@
       <c r="C33" s="2">
         <v>266.93</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1380,7 +1354,7 @@
       <c r="C34" s="2">
         <v>311.32</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1394,7 +1368,7 @@
       <c r="C35" s="2">
         <v>341.01</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1408,7 +1382,7 @@
       <c r="C36" s="2">
         <v>111.12</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1422,7 +1396,7 @@
       <c r="C37" s="2">
         <v>155.66</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1436,7 +1410,7 @@
       <c r="C38" s="2">
         <v>207.54</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1450,7 +1424,7 @@
       <c r="C39" s="2">
         <v>255.03</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1464,7 +1438,7 @@
       <c r="C40" s="2">
         <v>299.56</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1478,7 +1452,7 @@
       <c r="C41" s="2">
         <v>345.58</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1492,7 +1466,7 @@
       <c r="C42" s="2">
         <v>390.12</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1506,7 +1480,7 @@
       <c r="C43" s="2">
         <v>437.60</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1520,7 +1494,7 @@
       <c r="C44" s="2">
         <v>489.48</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1534,7 +1508,7 @@
       <c r="C45" s="2">
         <v>163</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1548,7 +1522,7 @@
       <c r="C46" s="2">
         <v>229.82</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1562,7 +1536,7 @@
       <c r="C47" s="2">
         <v>303.97</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1576,7 +1550,7 @@
       <c r="C48" s="2">
         <v>370.79</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1590,7 +1564,7 @@
       <c r="C49" s="2">
         <v>452.28</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1604,7 +1578,7 @@
       <c r="C50" s="2">
         <v>519.10</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1618,7 +1592,7 @@
       <c r="C51" s="2">
         <v>593.25</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1632,7 +1606,7 @@
       <c r="C52" s="2">
         <v>660.07</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1646,7 +1620,7 @@
       <c r="C53" s="2">
         <v>730.69</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="2" t="s">
         <v>37</v>
       </c>
     </row>

--- a/Side Bar Files/GWD Data/Electrical Essentials.xlsx
+++ b/Side Bar Files/GWD Data/Electrical Essentials.xlsx
@@ -878,7 +878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6397824-B5C6-47E4-851F-6BBC5B6BBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003454BB-01CF-4CC4-9B1D-9EB31E92BAA6}">
   <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Electrical Essentials.xlsx
+++ b/Side Bar Files/GWD Data/Electrical Essentials.xlsx
@@ -878,7 +878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003454BB-01CF-4CC4-9B1D-9EB31E92BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B8C88F-16DC-47E6-B857-CC2D9594BAA6}">
   <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
